--- a/j80_3000_pinout_I2C1.xlsx
+++ b/j80_3000_pinout_I2C1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Desktop\J80-3000\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68C2AF9-46D3-4B41-8848-31FD3A003C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6091738-88D4-448F-AFCA-1BEF80BBCF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="12645" activeTab="2" xr2:uid="{50F1D8E5-7FDD-4258-BBF0-30C61D1CF90C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{50F1D8E5-7FDD-4258-BBF0-30C61D1CF90C}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinout" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="265">
   <si>
     <t>COL/ROW/LED</t>
   </si>
@@ -641,42 +641,6 @@
   </si>
   <si>
     <t>D2</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>B13</t>
-  </si>
-  <si>
-    <t>B14</t>
-  </si>
-  <si>
-    <t>B15</t>
-  </si>
-  <si>
-    <t>A8</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>A11</t>
-  </si>
-  <si>
-    <t>A12</t>
-  </si>
-  <si>
-    <t>A15</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>B9</t>
   </si>
   <si>
     <t>5V</t>
@@ -804,15 +768,6 @@
     <t>Connected to</t>
   </si>
   <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
     <t>WeAct
 Blackpill
 STM32F411CUE6
@@ -840,10 +795,52 @@
     <t>PA1</t>
   </si>
   <si>
-    <t>ROW 11</t>
-  </si>
-  <si>
-    <t>ROW 12</t>
+    <t>PB2</t>
+  </si>
+  <si>
+    <t>PA7</t>
+  </si>
+  <si>
+    <t>PA6</t>
+  </si>
+  <si>
+    <t>PA5</t>
+  </si>
+  <si>
+    <t>PA4</t>
+  </si>
+  <si>
+    <t>PA2</t>
+  </si>
+  <si>
+    <t>PC15</t>
+  </si>
+  <si>
+    <t>PC13</t>
+  </si>
+  <si>
+    <t>PA8</t>
+  </si>
+  <si>
+    <t>PA9</t>
+  </si>
+  <si>
+    <t>PA10</t>
+  </si>
+  <si>
+    <t>PA11</t>
+  </si>
+  <si>
+    <t>PA12</t>
+  </si>
+  <si>
+    <t>PB4</t>
+  </si>
+  <si>
+    <t>PB6</t>
+  </si>
+  <si>
+    <t>PB7</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1435,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -1452,7 +1449,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
         <v>44</v>
@@ -1550,7 +1547,7 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="D21" t="s">
         <v>64</v>
@@ -1564,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D22" t="s">
         <v>66</v>
@@ -1694,82 +1691,82 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="5" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="G1" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="I1" s="6"/>
       <c r="J1" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="N1" s="6"/>
       <c r="O1" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="L2" t="s">
         <v>201</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="L2" t="s">
-        <v>213</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
         <v>189</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>202</v>
+        <v>49</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" t="s">
@@ -1784,26 +1781,26 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>203</v>
+        <v>52</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>188</v>
@@ -1814,32 +1811,32 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D5" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>54</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="M5" t="s">
         <v>33</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O5" t="s">
         <v>35</v>
@@ -1847,47 +1844,47 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="M7" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O7" t="s">
         <v>29</v>
@@ -1895,36 +1892,36 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
         <v>24</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O8" t="s">
         <v>26</v>
@@ -1932,13 +1929,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>81</v>
@@ -1948,26 +1945,26 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="2" t="s">
@@ -1978,17 +1975,17 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" t="s">
-        <v>194</v>
+        <v>251</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N10" s="2"/>
     </row>
@@ -2010,29 +2007,29 @@
         <v>84</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="2" t="s">
@@ -2045,29 +2042,29 @@
         <v>87</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" t="s">
-        <v>80</v>
+        <v>253</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="2" t="s">
@@ -2079,20 +2076,20 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="M13" t="s">
         <v>8</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O13" t="s">
         <v>10</v>
@@ -2100,10 +2097,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="2" t="s">
@@ -2116,29 +2113,29 @@
         <v>62</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>60</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" t="s">
-        <v>74</v>
+        <v>254</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="2" t="s">
@@ -2157,23 +2154,23 @@
         <v>190</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>40</v>
+        <v>263</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" t="s">
-        <v>89</v>
+        <v>248</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>264</v>
+        <v>65</v>
       </c>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="2" t="s">
@@ -2192,14 +2189,14 @@
         <v>191</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>265</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -2214,26 +2211,26 @@
         <v>90</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>67</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>211</v>
+        <v>68</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -2249,26 +2246,26 @@
         <v>87</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>70</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>212</v>
+        <v>71</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" t="s">
         <v>255</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N18" s="2"/>
     </row>
@@ -2284,23 +2281,23 @@
         <v>84</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" t="s">
-        <v>254</v>
+        <v>6</v>
       </c>
       <c r="M19" t="s">
         <v>4</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O19" t="s">
         <v>7</v>
@@ -2321,17 +2318,17 @@
         <v>57</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>189</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N20" s="2"/>
     </row>
@@ -2344,23 +2341,23 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="2" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="N21" s="2"/>
     </row>
@@ -2373,10 +2370,10 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="2" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -2388,10 +2385,10 @@
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="2" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -2403,10 +2400,10 @@
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="2" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -2424,27 +2421,27 @@
         <v>54</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="N25" s="6"/>
       <c r="O25" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -2465,19 +2462,19 @@
         <v>5</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>188</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s">
         <v>196</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -2508,7 +2505,7 @@
         <v>197</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -2529,7 +2526,7 @@
         <v>5</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>190</v>
@@ -2539,7 +2536,7 @@
         <v>198</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -2548,7 +2545,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>191</v>
@@ -2558,7 +2555,7 @@
         <v>199</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -2566,7 +2563,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>192</v>
@@ -2576,12 +2573,15 @@
         <v>200</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G31" t="s">
+        <v>59</v>
+      </c>
       <c r="H31" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>57</v>
@@ -2594,21 +2594,24 @@
         <v>43</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N31" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O31" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>90</v>
+      </c>
       <c r="H32" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>89</v>
@@ -2618,13 +2621,13 @@
         <v>40</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="N32" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O32" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.25">
@@ -2632,7 +2635,7 @@
         <v>75</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>73</v>
@@ -2645,13 +2648,13 @@
         <v>37</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="N33" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O33" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="7:15" x14ac:dyDescent="0.25">
@@ -2659,7 +2662,7 @@
         <v>78</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>76</v>
@@ -2672,13 +2675,13 @@
         <v>31</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N34" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O34" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.25">
@@ -2686,7 +2689,7 @@
         <v>81</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>79</v>
@@ -2699,18 +2702,18 @@
         <v>22</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O35" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="7:15" x14ac:dyDescent="0.25">
       <c r="I36" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>193</v>
@@ -2720,18 +2723,18 @@
         <v>19</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="N36" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O36" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="7:15" x14ac:dyDescent="0.25">
       <c r="I37" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>194</v>
@@ -2741,18 +2744,18 @@
         <v>16</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="N37" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O37" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="7:15" x14ac:dyDescent="0.25">
       <c r="I38" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>195</v>
@@ -2762,13 +2765,13 @@
         <v>13</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="N38" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="O38" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2797,7 +2800,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2852,10 +2855,10 @@
         <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>262</v>
+        <v>13</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>263</v>
+        <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>43</v>
@@ -3031,7 +3034,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -3078,7 +3081,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
